--- a/equipment_seed.xlsx
+++ b/equipment_seed.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +39,12 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +57,13 @@
         <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -68,16 +77,36 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,396 +472,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>zone</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>circle</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>division</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sub_division</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>substation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>RT North Division</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>RT North SD3 Devanahalli</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>BIAL Begur Section</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>BRAZ</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Begur</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>220kV BIAL Begur</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>RT East Division</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>RT East SD4 Anekal</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>EDC Section</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>220kV EDC</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>BMAZ South</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Hoody</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>RT East Division</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>RT East SD4 Anekal</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jigani Section</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Ramanagara</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Yerandanahally</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>220kV Jigani</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>RT South Division</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>RT South SD4 Kanakapura</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Kanakapura Section</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>220kV Kanakapura</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Ramanagara</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Kanakapura</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Kolar Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Kolar Division</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Kolar SD1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Kolar Town Section</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>BRAZ</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kolar</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>220kV Kolar</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Kolar Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Kolar Division</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Malur SD</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Malur Section</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>BRAZ</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Malur</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>220kV Malur</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>RT North Division</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>RT North SD2 Hebbal</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Manyatha Tech Park Section</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>220kV Manyatha Tech Park</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>BMAZ North</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Hebbal</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>RT South Division</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>RT South SD1 Rajajinagar</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Rajajinagar Section</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>BMAZ North</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>NRS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>220kV NRS Rajajinagar</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>RT East Division</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>RT East SD1 Whitefield</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Sarjapura Section</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Ramanagara</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Yerandanahally</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>220kV Sarjapura</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>RT East Division</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>RT East SD1 Whitefield</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>DHP Section</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>400kV DHP</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>BRAZ</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Devanahalli Hardware Park</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Zone</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru Transmission Circle</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>RT East Division</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>RT East SD1 Whitefield</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Hoody Section</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Zone</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>BMAZ South</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Hoody</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>400kV Hoody</t>
         </is>
@@ -850,7 +759,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P495"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -4053,7 +3962,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4115,7 +4024,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4177,7 +4086,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -4239,7 +4148,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4301,7 +4210,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4363,7 +4272,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4425,7 +4334,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4487,7 +4396,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4549,7 +4458,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4611,7 +4520,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4673,7 +4582,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4735,7 +4644,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4797,7 +4706,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4859,7 +4768,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4921,7 +4830,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4983,7 +4892,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -5045,7 +4954,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -5107,7 +5016,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5169,7 +5078,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -5227,7 +5136,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -5285,7 +5194,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -5343,7 +5252,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5401,7 +5310,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5459,7 +5368,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5517,7 +5426,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5579,7 +5488,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5641,7 +5550,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5703,7 +5612,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5765,7 +5674,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5827,7 +5736,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5889,7 +5798,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5951,7 +5860,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -6013,7 +5922,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -6075,7 +5984,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -6137,7 +6046,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -6199,7 +6108,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -6261,7 +6170,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -6323,7 +6232,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -6385,7 +6294,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -6447,7 +6356,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -6509,7 +6418,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -6571,7 +6480,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6633,7 +6542,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6691,7 +6600,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6749,7 +6658,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6807,7 +6716,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6865,7 +6774,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6923,7 +6832,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6981,7 +6890,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -7047,7 +6956,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -7113,7 +7022,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -7179,7 +7088,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -9519,7 +9428,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -9581,7 +9490,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -9643,7 +9552,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -9705,7 +9614,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -9767,7 +9676,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -9829,7 +9738,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -9891,7 +9800,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -9953,7 +9862,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -10015,7 +9924,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -10077,7 +9986,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -10139,7 +10048,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -10201,7 +10110,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -10263,7 +10172,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -10321,7 +10230,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -10379,7 +10288,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -10437,7 +10346,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -10495,7 +10404,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -10553,7 +10462,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -10611,7 +10520,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -10673,7 +10582,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -10735,7 +10644,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -10797,7 +10706,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10859,7 +10768,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -10921,7 +10830,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -10983,7 +10892,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -11045,7 +10954,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -11107,7 +11016,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -11169,7 +11078,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -11231,7 +11140,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -11293,7 +11202,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -11355,7 +11264,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -11413,7 +11322,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -11471,7 +11380,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -11529,7 +11438,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -11587,7 +11496,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -11645,7 +11554,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -11703,7 +11612,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -11765,7 +11674,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Kanakpura</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -16545,7 +16454,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -16607,7 +16516,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -16669,7 +16578,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -16731,7 +16640,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -16793,7 +16702,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -16855,7 +16764,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -16917,7 +16826,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -16979,7 +16888,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -17041,7 +16950,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -17103,7 +17012,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -17165,7 +17074,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -17227,7 +17136,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -17289,7 +17198,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -17351,7 +17260,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -17413,7 +17322,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -17475,7 +17384,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -17537,7 +17446,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -17599,7 +17508,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -17661,7 +17570,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -17723,7 +17632,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -17785,7 +17694,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -17847,7 +17756,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -17909,7 +17818,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -17971,7 +17880,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -18033,7 +17942,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -18095,7 +18004,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -18157,7 +18066,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -18219,7 +18128,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -18281,7 +18190,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -18343,7 +18252,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -18405,7 +18314,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -18467,7 +18376,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -18529,7 +18438,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -18591,7 +18500,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -18653,7 +18562,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -18715,7 +18624,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -18777,7 +18686,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -18839,7 +18748,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -18901,7 +18810,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -18963,7 +18872,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -19025,7 +18934,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -19087,7 +18996,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -19149,7 +19058,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -19215,7 +19124,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -19281,7 +19190,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -19347,7 +19256,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -26623,7 +26532,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -26685,7 +26594,7 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -26747,7 +26656,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -26809,7 +26718,7 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -26867,7 +26776,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -26925,7 +26834,7 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -26983,7 +26892,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -27045,7 +26954,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -27107,7 +27016,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -27169,7 +27078,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -27231,7 +27140,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -27293,7 +27202,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -27355,7 +27264,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -27417,7 +27326,7 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -27479,7 +27388,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -27541,7 +27450,7 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -27603,7 +27512,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -27665,7 +27574,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -27727,7 +27636,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -27789,7 +27698,7 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -27851,7 +27760,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -27913,7 +27822,7 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -27975,7 +27884,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -28037,7 +27946,7 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -28099,7 +28008,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -28161,7 +28070,7 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -28223,7 +28132,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -28285,7 +28194,7 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -28347,7 +28256,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -28409,7 +28318,7 @@
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -28471,7 +28380,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -28533,7 +28442,7 @@
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -28595,7 +28504,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -28657,7 +28566,7 @@
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -28715,7 +28624,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -28773,7 +28682,7 @@
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -28831,7 +28740,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -28889,7 +28798,7 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -28947,7 +28856,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -29005,7 +28914,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -29059,7 +28968,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>400kV Devanahalli Hardware Park</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">

--- a/equipment_seed.xlsx
+++ b/equipment_seed.xlsx
@@ -18,13 +18,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P495"/>
+  <dimension ref="A1:P496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3471,12 +3476,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>25-Nov-2006</t>
+          <t>26-Jan-2007</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HT1690/1225 69</t>
+          <t>HT-1690/12569</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3496,62 +3501,62 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>220kV BIAL Begur</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>Power Transformer</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>220/66/11kV</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>100MVA Power TR-3</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Kanohar Electrical Ltd</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>07-Nov-2022</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>KT-100000/O- 2/2</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>100MVA Power TR-2</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="n"/>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>EMCO</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>17-Jul-2007</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>HT-1690/12570</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="n"/>
+      <c r="K51" s="1" t="n"/>
+      <c r="L51" s="1" t="n"/>
+      <c r="M51" s="1" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="1" t="inlineStr">
         <is>
           <t>YNyn0d11</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
+      <c r="O51" s="1" t="n"/>
+      <c r="P51" s="1" t="inlineStr">
         <is>
           <t>In-service</t>
         </is>
@@ -3570,32 +3575,47 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20MVA Power TR-2</t>
+          <t>100MVA Power TR-3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IMP Powers Ltd</t>
+          <t>Kanohar Electrical Ltd</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>30-Jun-2017</t>
+          <t>07-Nov-2022</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KT-100000/51</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>19.6</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -3607,52 +3627,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV BIAL Begur</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HAL line</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>20MVA Power TR-2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2008</t>
+          <t>IMP Powers Ltd</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>20-Dec-2010</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>1200-800/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>30-Jun-2017</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -3684,7 +3694,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3741,7 +3751,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3793,12 +3803,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NIMHANS 220 kV line</t>
+          <t>HAL line</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3818,7 +3828,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
+          <t>1200-800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3855,7 +3865,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3912,7 +3922,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3964,12 +3974,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A station line</t>
+          <t>NIMHANS 220 kV line</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4026,7 +4036,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4083,7 +4093,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4135,12 +4145,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>A station line</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4160,12 +4170,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>600-300/1-1-1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4197,7 +4207,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4254,7 +4264,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4306,12 +4316,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4368,7 +4378,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4425,7 +4435,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4477,12 +4487,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4502,12 +4512,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
+          <t>600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -4539,7 +4549,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4596,7 +4606,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4638,7 +4648,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4648,17 +4658,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alstom</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4671,9 +4681,14 @@
           <t>20-Dec-2010</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V-110V</t>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1200-600-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -4705,7 +4720,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4757,7 +4772,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4804,12 +4819,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4861,7 +4876,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4913,7 +4928,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4950,27 +4965,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BMTC line</t>
+          <t>Bus-2/Transfer Bus</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Alstom</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4983,14 +4998,9 @@
           <t>20-Dec-2010</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>1200-800/1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>800/1-1-1-1A</t>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5022,7 +5032,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5079,7 +5089,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5131,12 +5141,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B station line</t>
+          <t>BMTC line</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5193,7 +5203,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5250,7 +5260,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5302,12 +5312,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Austin line</t>
+          <t>B station line</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5364,7 +5374,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5421,7 +5431,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5473,12 +5483,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>Austin line</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5498,12 +5508,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>1200-800/1-1-1-1A</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1600/1-1-1A</t>
+          <t>800/1-1-1-1A</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -5535,7 +5545,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5592,7 +5602,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5644,12 +5654,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5706,7 +5716,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5763,7 +5773,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5815,12 +5825,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5840,7 +5850,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1600-1200/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5877,7 +5887,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5934,7 +5944,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5976,7 +5986,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5986,17 +5996,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alstom</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6009,9 +6019,14 @@
           <t>20-Dec-2010</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V</t>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1600-1200/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1600/1-1-1A</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -6043,7 +6058,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6095,7 +6110,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6142,12 +6157,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6199,7 +6214,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6251,7 +6266,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6288,22 +6303,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>150MVA</t>
+          <t>Bus-2/Transfer Bus</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Power TR-1 ABB</t>
+          <t>Alstom</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6316,24 +6336,9 @@
           <t>20-Dec-2010</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>13074-002</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>17.5</t>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -6365,7 +6370,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Power TR-2 ABB</t>
+          <t>Power TR-1 ABB</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6380,7 +6385,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>13074-001</t>
+          <t>13074-002</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6417,17 +6422,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>31.5MVA</t>
+          <t>150MVA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Power TR-2 EMCO</t>
+          <t>Power TR-2 ABB</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6442,22 +6447,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>13074-001</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -6489,12 +6494,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Power TR-3 EMCO</t>
+          <t>Power TR-2 EMCO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6504,7 +6509,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6531,32 +6536,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>220kV Jigani</t>
+          <t>220kV EDC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mylasandra Line 1 220Kv line</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>31.5MVA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Power TR-3 EMCO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6566,17 +6566,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>04-Mar-2018</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>800-600-400-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>20-Dec-2010</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>12.6</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -6608,7 +6618,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6665,7 +6675,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6717,12 +6727,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>Mylasandra Line 1 220Kv line</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6732,7 +6742,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6747,7 +6757,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -6779,7 +6789,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6836,7 +6846,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6888,12 +6898,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6908,7 +6918,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>15-Nov-2019</t>
+          <t>04-Mar-2018</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6950,7 +6960,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7007,7 +7017,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7059,12 +7069,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7074,12 +7084,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01-Sep-2021</t>
+          <t>15-Nov-2019</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7089,7 +7099,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -7121,7 +7131,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7136,7 +7146,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>04-Mar-2018</t>
+          <t>01-Sep-2021</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7178,7 +7188,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7193,7 +7203,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01-Sep-2021</t>
+          <t>04-Mar-2018</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7220,7 +7230,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7230,32 +7240,37 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Main Bus-2</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SCT Ltd,Ghaziabad</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>27-May-2022</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V</t>
+          <t>01-Sep-2021</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>800-600-400-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -7287,7 +7302,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7339,7 +7354,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7376,47 +7391,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KUMBARANAHALLI L1 line</t>
+          <t>Main Bus-2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>SCT Ltd,Ghaziabad</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>30-Sep-2011</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>800-400/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>800/1-1-1A</t>
+          <t>27-May-2022</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -7448,7 +7458,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7505,7 +7515,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7557,17 +7567,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JIGANI O/G line</t>
+          <t>KUMBARANAHALLI L1 line</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7577,12 +7587,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>15-Nov-2019</t>
+          <t>30-Sep-2011</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>800-600-400-200/1-1-1A</t>
+          <t>800-400/1-1-1A</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7619,7 +7629,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7676,7 +7686,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7728,37 +7738,37 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>JIGANI O/G line</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>04-Mar-2018</t>
+          <t>15-Nov-2019</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1600-1200-1000/1-1-1A</t>
+          <t>800-600-400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>1600/1-1-1A</t>
+          <t>800/1-1-1A</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -7790,7 +7800,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7847,7 +7857,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7899,12 +7909,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7914,17 +7924,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01-Sep-2021</t>
+          <t>04-Mar-2018</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>1600-1200/1-1-1A</t>
+          <t>1600-1200-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7961,7 +7971,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8018,7 +8028,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8060,7 +8070,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8070,12 +8080,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Main Bus-1</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8090,12 +8100,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>30-Sep-2011</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V-110V</t>
+          <t>01-Sep-2021</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>1600-1200/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>1600/1-1-1A</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -8127,7 +8142,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8179,7 +8194,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8226,12 +8241,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Main Bus-2</t>
+          <t>Main Bus-1</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8246,7 +8261,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>20-Oct-2020</t>
+          <t>30-Sep-2011</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8283,22 +8298,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Suman Control Pvt Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>20-Oct-2021</t>
+          <t>20-Oct-2020</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8335,22 +8350,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>Suman Control Pvt Ltd</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>20-Oct-2020</t>
+          <t>20-Oct-2021</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8372,22 +8387,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>150MVA</t>
+          <t>Main Bus-2</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Power TR-1 ABB</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8397,27 +8417,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>04-Mar-2018</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>13068-005</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>13.5</t>
+          <t>20-Oct-2020</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -8449,7 +8454,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Power TR-2 ABB</t>
+          <t>Power TR-1 ABB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8459,12 +8464,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>15-Nov-2019</t>
+          <t>04-Mar-2018</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>13068-06</t>
+          <t>13068-005</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -8501,47 +8506,47 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>31.5MVA</t>
+          <t>150MVA</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Power TR-1 Victory Electricals Ltd</t>
+          <t>Power TR-2 ABB</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>30-Sep-2011</t>
+          <t>15-Nov-2019</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4-0012/6</t>
+          <t>13068-06</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -8573,22 +8578,22 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Power TR-2 Bharat Bijlee Ltd</t>
+          <t>Power TR-1 Victory Electricals Ltd</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>03-Nov-2022</t>
+          <t>30-Sep-2011</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4934/17</t>
+          <t>4-0012/6</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -8603,7 +8608,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -8615,52 +8620,57 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>220kV Jigani</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Kanakapura-Somanahalli line</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>31.5MVA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Power TR-2 Bharat Bijlee Ltd</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01-Aug-2008</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>800-600-400-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>03-Nov-2022</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>4934/17</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>9.7</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -8692,7 +8702,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8749,7 +8759,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8801,12 +8811,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Kanakapura-TkHalli line</t>
+          <t>Kanakapura-Somanahalli line</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8863,7 +8873,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8920,7 +8930,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8972,12 +8982,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>Kanakapura-TkHalli line</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8992,7 +9002,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01-Jan-2008</t>
+          <t>01-Aug-2008</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9002,7 +9012,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>300/1-1-1-1-1A</t>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -9034,7 +9044,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9091,7 +9101,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9143,12 +9153,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9173,7 +9183,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -9205,7 +9215,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9262,7 +9272,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9304,7 +9314,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9314,17 +9324,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9337,9 +9347,14 @@
           <t>01-Jan-2008</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V-110V</t>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>800-600-400-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -9371,7 +9386,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9423,7 +9438,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9470,12 +9485,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9527,7 +9542,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9579,7 +9594,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9616,27 +9631,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Kanakapura line</t>
+          <t>Bus-2/Transfer Bus</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9649,14 +9664,9 @@
           <t>01-Jan-2008</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>400-200/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>400/1-1-1A</t>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -9688,7 +9698,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -9745,7 +9755,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9797,12 +9807,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>Kanakapura line</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9822,12 +9832,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1200-1000-800-600/1-1-1A</t>
+          <t>400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -9859,7 +9869,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9916,7 +9926,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9968,32 +9978,32 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>100MVA Power TR-2</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SCT Ltd,Ghaziabad</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>24-Jul-2017</t>
+          <t>01-Jan-2008</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>1200-1000-800-600/1-1-1A</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10030,7 +10040,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10087,7 +10097,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10139,32 +10149,32 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>100MVA Power TR-2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>SCT Ltd,Ghaziabad</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01-Jan-2008</t>
+          <t>24-Jul-2017</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>1000-800-600/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10201,7 +10211,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10258,7 +10268,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10300,7 +10310,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10310,17 +10320,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vidyuth Controls Systems Pvt Ltd</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10333,9 +10343,14 @@
           <t>01-Jan-2008</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V-110V</t>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>1000-800-600/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -10367,7 +10382,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10419,7 +10434,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10466,12 +10481,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10523,7 +10538,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10575,7 +10590,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10612,27 +10627,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>100MVA</t>
+          <t>Bus-2/Transfer Bus</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Power TR-1 ABB</t>
+          <t>Vidyuth Controls Systems Pvt Ltd</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -10640,19 +10660,9 @@
           <t>01-Jan-2008</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>13044-002</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -10684,22 +10694,22 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Power TR-2 BHEL</t>
+          <t>Power TR-1 ABB</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>24-Jul-2017</t>
+          <t>01-Jan-2008</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2141612</t>
+          <t>13044-002</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -10721,52 +10731,52 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>220kV Kolar</t>
+          <t>220kV Kanakapura</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PGCIL line-1 220kV line</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>100MVA</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>Power TR-2 BHEL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>11-Feb-2013</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>24-Jul-2017</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2141612</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>YNyn0d11</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -10798,7 +10808,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10855,7 +10865,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10870,7 +10880,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>11-Feb-1998</t>
+          <t>11-Feb-2013</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10907,12 +10917,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PGCIL line-2 220kV line</t>
+          <t>PGCIL line-1 220kV line</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10927,7 +10937,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>11-Feb-2013</t>
+          <t>11-Feb-1998</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10969,7 +10979,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10984,7 +10994,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>11-Feb-2003</t>
+          <t>11-Feb-2013</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11026,7 +11036,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11068,7 +11078,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11078,12 +11088,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Main Bus</t>
+          <t>PGCIL line-2 220kV line</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11091,14 +11101,24 @@
           <t>BHEL</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>21-Aug-1989</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V</t>
+          <t>11-Feb-2003</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>1200-600-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -11130,7 +11150,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11162,47 +11182,37 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangarpet line-1 line</t>
+          <t>Main Bus</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>LAMCO</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2015</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>18-May-2023</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>800-400/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>400/1-1-1A</t>
+          <t>21-Aug-1989</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -11229,37 +11239,37 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20MVA Power TR-2</t>
+          <t>Bangarpet line-1 line</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>&amp; Electrical</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>29-Nov-1991</t>
+          <t>18-May-2023</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>400-200-100/1-1-1A</t>
+          <t>800-400/1-1-1A</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>200/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -11291,7 +11301,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11343,37 +11353,37 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>100MVA Power TR-3</t>
+          <t>20MVA Power TR-2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>&amp; Electrical</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>08-Dec-2016</t>
+          <t>29-Nov-1991</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>400-200-100/1-1-1A</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>200/1-1-1A</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -11405,7 +11415,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11462,7 +11472,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11514,32 +11524,32 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>100MVA Power TR-3</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>21-Aug-1995</t>
+          <t>08-Dec-2016</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>1000-800-600/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11576,7 +11586,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11633,7 +11643,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11675,7 +11685,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11685,27 +11695,37 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Main Bus-1</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Thirumalai industries Bangalore</t>
+          <t>Powergear Ltd</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>1995</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>21-Aug-1989</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V</t>
+          <t>21-Aug-1995</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>1000-800-600/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -11737,7 +11757,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11779,17 +11799,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Main Bus-2</t>
+          <t>Main Bus-1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Thirumalai industries Bangalore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -11816,27 +11836,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>100MVA</t>
+          <t>Main Bus-2</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Power TR-1 NGEF</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>1989</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -11844,19 +11864,9 @@
           <t>21-Aug-1989</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>680000059</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -11888,22 +11898,22 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Power TR-2 NGEF</t>
+          <t>Power TR-1 NGEF</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>08-Sep-2021</t>
+          <t>21-Aug-1989</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>6800000136</t>
+          <t>680000059</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -11914,11 +11924,6 @@
       <c r="N201" t="inlineStr">
         <is>
           <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -11950,22 +11955,22 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Power TR-3 Bharat Bijlee Ltd</t>
+          <t>Power TR-2 NGEF</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>12-Sep-2025</t>
+          <t>08-Sep-2021</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>5867/02</t>
+          <t>6800000136</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -11980,7 +11985,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -12002,42 +12007,47 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20MVA</t>
+          <t>100MVA</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Power TR-1 Andrewyule</t>
+          <t>Power TR-3 Bharat Bijlee Ltd</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>26-Mar-2004</t>
+          <t>12-Sep-2025</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>5867/02</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>10.2</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -12069,22 +12079,22 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Power TR-2 IMP Powers Ltd</t>
+          <t>Power TR-1 Andrewyule</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>22-Aug-2017</t>
+          <t>26-Mar-2004</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>PT-7761</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -12095,11 +12105,6 @@
       <c r="N204" t="inlineStr">
         <is>
           <t>Dyn11</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -12111,52 +12116,57 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>220kV Malur</t>
+          <t>220kV Kolar</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Malur-Kolar Line-1 line</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>20MVA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>Power TR-2 IMP Powers Ltd</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>13-Apr-2009</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>22-Aug-2017</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>PT-7761</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -12188,7 +12198,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -12203,7 +12213,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>22-Sep-1999</t>
+          <t>13-Apr-2009</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12245,7 +12255,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -12297,12 +12307,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Malur-Hoody Line line</t>
+          <t>Malur-Kolar Line-1 line</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -12359,7 +12369,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -12416,7 +12426,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12468,12 +12478,12 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Power TR-1</t>
+          <t>Malur-Hoody Line line</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -12493,12 +12503,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>1200-800-600-300/1-1-1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>300/1-1-1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -12530,7 +12540,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -12587,7 +12597,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -12639,12 +12649,12 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Power TR-2</t>
+          <t>Power TR-1</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -12664,7 +12674,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
+          <t>1200-800-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12701,7 +12711,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -12758,7 +12768,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -12810,12 +12820,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>Power TR-2</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12835,12 +12845,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>1200-800-600-300/1-1-1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -12872,7 +12882,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12929,7 +12939,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12971,27 +12981,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Automatic Electric Ltd</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13004,9 +13014,14 @@
           <t>22-Sep-1999</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V-110V</t>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>1200-800-600-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -13038,7 +13053,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13090,7 +13105,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13137,12 +13152,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -13194,22 +13209,22 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Suman Control Pvt Ltd</t>
+          <t>Automatic Electric Ltd</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
+          <t>22-Sep-1999</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13246,22 +13261,22 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Automatic Electric Ltd</t>
+          <t>Suman Control Pvt Ltd</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>22-Sep-1999</t>
+          <t>06-Oct-2025</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13288,37 +13303,37 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus-2/Transfer Bus</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C G Power</t>
+          <t>Automatic Electric Ltd</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>24-Nov-2019</t>
+          <t>22-Sep-1999</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>220kV/110V-110V</t>
+          <t>66kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -13350,7 +13365,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -13402,7 +13417,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -13439,47 +13454,42 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Kgf Line-1 line</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mechanical Engg.</t>
+          <t>C G Power</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>19-Apr-2024</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>800-400/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>400/1-1-1A</t>
+          <t>24-Nov-2019</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -13511,7 +13521,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -13568,7 +13578,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -13620,37 +13630,37 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Kgf Line-2 line</t>
+          <t>Kgf Line-1 line</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Mechanical Engg.</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>22-Sep-1999</t>
+          <t>19-Apr-2024</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>800-400/1-1-1A</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>300/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -13682,7 +13692,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -13739,7 +13749,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -13791,37 +13801,37 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Hoskote Line-1 line</t>
+          <t>Kgf Line-2 line</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mechanical Engg.</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>19-Apr-2024</t>
+          <t>22-Sep-1999</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>800-400/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>400/1-1-1A</t>
+          <t>300/1-1-1A</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -13853,7 +13863,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -13910,7 +13920,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -13962,37 +13972,37 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Hoskote Line-2 line</t>
+          <t>Hoskote Line-1 line</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Mechanical Engg.</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>22-Sep-1999</t>
+          <t>19-Apr-2024</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>800-400/1-1-1A</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>300/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -14024,7 +14034,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -14081,7 +14091,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -14133,12 +14143,12 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Malur Line line</t>
+          <t>Hoskote Line-2 line</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -14195,7 +14205,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -14252,7 +14262,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -14304,17 +14314,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Masthi Line line</t>
+          <t>Malur Line line</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Power Switchgear</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -14366,7 +14376,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -14423,7 +14433,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -14475,37 +14485,37 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Lakkur line line</t>
+          <t>Masthi Line line</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>Power Switchgear</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>31-Dec-2021</t>
+          <t>22-Sep-1999</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>400-200/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>400/1-1-1A</t>
+          <t>300/1-1-1A</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -14537,7 +14547,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -14594,7 +14604,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -14646,37 +14656,37 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Power TR-1</t>
+          <t>Lakkur line line</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>10-Mar-2006</t>
+          <t>31-Dec-2021</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>1000-600/1-1-1A</t>
+          <t>400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -14708,22 +14718,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mechanical Engg.</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>02-Feb-2025</t>
+          <t>10-Mar-2006</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14765,22 +14775,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Mechanical Engg.</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>08-Mar-2019</t>
+          <t>02-Feb-2025</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14817,12 +14827,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>30MVAR Cap Bank-1</t>
+          <t>Power TR-1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -14832,22 +14842,22 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>09-Jan-2001</t>
+          <t>08-Mar-2019</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>400-200/1-1-1A</t>
+          <t>1000-600/1-1-1A</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>400/1-1-1A</t>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
@@ -14879,7 +14889,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -14921,52 +14931,47 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>30MVAR Cap Bank-1</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>TR-1 ABB</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>10-Mar-2006</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>13024/002</t>
-        </is>
-      </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>09-Jan-2001</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>400-200/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -14998,22 +15003,22 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TR-2 APEX</t>
+          <t>TR-1 ABB</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>22-Sep-1999</t>
+          <t>10-Mar-2006</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>T-1035/03</t>
+          <t>13024/002</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -15028,7 +15033,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -15040,52 +15045,57 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Malur</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Hebbal 220kV BAY line</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>TR-2 APEX</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>20-May-2019</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>1200-600/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>22-Sep-1999</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>T-1035/03</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>YNyn0d11</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>9.3</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -15117,7 +15127,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -15174,7 +15184,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -15226,12 +15236,12 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>HOODY LINE line</t>
+          <t>Hebbal 220kV BAY line</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -15288,7 +15298,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -15345,7 +15355,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -15397,12 +15407,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ITI LINE line</t>
+          <t>HOODY LINE line</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -15459,7 +15469,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -15516,7 +15526,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -15568,12 +15578,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>ITI LINE line</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -15593,12 +15603,12 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>600-300/1-1-1-1-1A</t>
+          <t>1200-600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -15630,7 +15640,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -15687,7 +15697,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -15739,12 +15749,12 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -15801,7 +15811,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -15858,7 +15868,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -15910,12 +15920,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-2</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -15935,12 +15945,12 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
+          <t>600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>1200/1-1-1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -15972,7 +15982,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -16029,7 +16039,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -16076,17 +16086,17 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ATTUR LINE line</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -16106,12 +16116,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>1200-800/1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>1200/1-1-1A</t>
+          <t>1200/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
@@ -16143,7 +16153,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -16200,7 +16210,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -16252,12 +16262,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>SAHAKARA NAGARA line</t>
+          <t>ATTUR LINE line</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -16314,7 +16324,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -16371,7 +16381,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -16423,12 +16433,12 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>MANYATHA AIS line</t>
+          <t>SAHAKARA NAGARA line</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -16485,7 +16495,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -16542,7 +16552,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -16594,12 +16604,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>SHOBA CITY line</t>
+          <t>MANYATHA AIS line</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -16656,7 +16666,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -16713,7 +16723,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -16765,12 +16775,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>SPARE LINE line</t>
+          <t>SHOBA CITY line</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -16827,7 +16837,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -16884,7 +16894,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -16936,12 +16946,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>150MVA Power TR-1</t>
+          <t>SPARE LINE line</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -16961,12 +16971,12 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>1200-800/1-1-1A</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>1600/1-1-1A</t>
+          <t>1200/1-1-1A</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
@@ -16998,7 +17008,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -17055,7 +17065,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -17107,12 +17117,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2</t>
+          <t>150MVA Power TR-1</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -17169,7 +17179,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -17226,7 +17236,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -17278,12 +17288,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>150MVA Power TR-2</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -17340,7 +17350,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -17397,7 +17407,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -17439,22 +17449,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>150MVA Power TR-2 GE T&amp;D India Limited 150.0 220/66/11kV YNyn0d11 14.6 2017 20-May-2019 In-service 31125</t>
+          <t>Bus Coupler</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3 31.5MVA Power TR-1 Indotech Transformers Ltd</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -17467,24 +17482,14 @@
           <t>20-May-2019</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>ITK-53552</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>Dyn11</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>12.5</t>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>1600-1000/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>1600/1-1-1A</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
@@ -17511,12 +17516,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>31.5MVA</t>
+          <t>150MVA Power TR-2 GE T&amp;D India Limited 150.0 220/66/11kV YNyn0d11 14.6 2017 20-May-2019 In-service 31125</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Power TR-2 Indotech Transformers Ltd</t>
+          <t>3 31.5MVA Power TR-1 Indotech Transformers Ltd</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -17531,7 +17536,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>ITK53553</t>
+          <t>ITK-53552</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -17578,7 +17583,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Power TR-3 Indotech Transformers Ltd</t>
+          <t>Power TR-2 Indotech Transformers Ltd</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -17593,7 +17598,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>ITK-53554</t>
+          <t>ITK53553</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -17640,7 +17645,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Power TR-4 Indotech Transformers Ltd</t>
+          <t>Power TR-3 Indotech Transformers Ltd</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -17655,7 +17660,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>ITK/53555</t>
+          <t>ITK-53554</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -17682,52 +17687,57 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>220kV NRS Rajajinagar</t>
+          <t>220kV Manyatha Tech Park</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Peenya line</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>31.5MVA</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>Power TR-4 Indotech Transformers Ltd</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>01-Jun-1998</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>20-May-2019</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>ITK/53555</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>12.5</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -17759,7 +17769,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -17816,7 +17826,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -17868,37 +17878,37 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Anand Rao circle line</t>
+          <t>Peenya line</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>AREVA</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>26-May-2010</t>
+          <t>01-Jun-1998</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>800-400/1-1-1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
@@ -17930,7 +17940,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -17987,7 +17997,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -18034,12 +18044,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>SRS2 (Mahalakshmi Layout)</t>
+          <t>Anand Rao circle line</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -18049,27 +18059,27 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Sri Venkateshwara</t>
+          <t>AREVA</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>19-Dec-2000</t>
+          <t>26-May-2010</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>400-200/1-1-1A</t>
+          <t>800-400/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>400/1-1-1A</t>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -18096,17 +18106,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>A2 line</t>
+          <t>SRS2 (Mahalakshmi Layout)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Sri Venkateshwara</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -18116,7 +18126,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>26-Dec-2000</t>
+          <t>19-Dec-2000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -18158,7 +18168,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -18205,42 +18215,42 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>A2 line</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>27-May-2007</t>
+          <t>26-Dec-2000</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>1200-600-300/1-1-1-1-1A</t>
+          <t>400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>600/1-1-1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
@@ -18272,7 +18282,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -18329,7 +18339,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -18381,12 +18391,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>100MVA Power TR-2</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -18401,7 +18411,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>05-Jun-1998</t>
+          <t>27-May-2007</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -18443,7 +18453,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -18500,7 +18510,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -18547,42 +18557,42 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>100MVA Power TR-2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>19-Feb-2019</t>
+          <t>05-Jun-1998</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>1200-600-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
@@ -18614,7 +18624,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -18671,7 +18681,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -18723,37 +18733,37 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20MVA Power TR-1</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>05-Jul-1998</t>
+          <t>19-Feb-2019</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>300/1-1-1A</t>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
@@ -18785,7 +18795,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -18805,7 +18815,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>300-150/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -18842,7 +18852,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -18862,7 +18872,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>300-150/1-1-1A</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -18894,12 +18904,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20MVA Power TR-4</t>
+          <t>20MVA Power TR-1</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -18914,7 +18924,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>14-Sep-1998</t>
+          <t>05-Jul-1998</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -18956,7 +18966,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -19013,7 +19023,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -19065,37 +19075,37 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20MVAR Cap Bank-1</t>
+          <t>20MVA Power TR-4</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>NNP (No name plate)</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>21-Jun-1984</t>
+          <t>14-Sep-1998</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>600-400-200-100/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>200/1-1-1A</t>
+          <t>300/1-1-1A</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
@@ -19127,7 +19137,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -19174,42 +19184,42 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Bank-5</t>
+          <t>20MVAR Cap Bank-1</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>AREVA</t>
+          <t>NNP (No name plate)</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>15-Sep-2008</t>
+          <t>21-Jun-1984</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>2000-1200/1-1-1A</t>
+          <t>600-400-200-100/1-1-1A</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>2000/1-1-1A</t>
+          <t>200/1-1-1A</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
@@ -19241,7 +19251,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -19298,7 +19308,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -19350,12 +19360,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Bank-5(A)</t>
+          <t>Bank-5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -19412,7 +19422,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -19469,7 +19479,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -19521,37 +19531,37 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>F4-DEVAIAH PARK</t>
+          <t>Bank-5(A)</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Instrans</t>
+          <t>AREVA</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>27-Sep-2006</t>
+          <t>15-Sep-2008</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>400-200/1-1A</t>
+          <t>2000-1200/1-1-1A</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>200/1-1A</t>
+          <t>2000/1-1-1A</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
@@ -19583,7 +19593,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -19640,7 +19650,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -19692,12 +19702,12 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>F10-SUBRAMANIYA NAGAR</t>
+          <t>F4-DEVAIAH PARK</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -19754,7 +19764,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -19811,7 +19821,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -19863,27 +19873,27 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>F13-R R RMU 6th Block , W3</t>
+          <t>F10-SUBRAMANIYA NAGAR</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Satlore Transformer</t>
+          <t>Instrans</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>18-Jul-2022</t>
+          <t>27-Sep-2006</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
@@ -19893,7 +19903,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>400/1-1A</t>
+          <t>200/1-1A</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
@@ -19920,27 +19930,27 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>F20-ESI</t>
+          <t>F13-R R RMU 6th Block , W3</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Instrans</t>
+          <t>Satlore Transformer</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>27-Sep-2006</t>
+          <t>18-Jul-2022</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
@@ -19982,7 +19992,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -20039,7 +20049,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -20091,12 +20101,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>F24-INDUSRIAL ESTATE</t>
+          <t>F20-ESI</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -20153,7 +20163,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -20205,12 +20215,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>F30-MAGADI ROAD</t>
+          <t>F24-INDUSRIAL ESTATE</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -20220,12 +20230,12 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>27-Sep-2007</t>
+          <t>27-Sep-2006</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -20267,7 +20277,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -20282,7 +20292,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>26-Jan-2019</t>
+          <t>27-Sep-2007</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -20324,7 +20334,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -20339,7 +20349,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>27-Sep-2007</t>
+          <t>26-Jan-2019</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -20366,42 +20376,47 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>11kV</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Main Bus</t>
+          <t>F30-MAGADI ROAD</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Mehru Electrical &amp; Mechanical Engg. Ltd</t>
+          <t>Instrans</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>18-Feb-2017</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V-110V</t>
+          <t>27-Sep-2007</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>400-200/1-1A</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>400/1-1A</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
@@ -20433,7 +20448,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -20470,47 +20485,42 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>A2 line</t>
+          <t>Main Bus</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>Mehru Electrical &amp; Mechanical Engg. Ltd</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>26-Dec-2000</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>400-200/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>400/1-1-1A</t>
+          <t>18-Feb-2017</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -20542,7 +20552,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -20594,37 +20604,37 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>A2 line</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>19-Feb-2019</t>
+          <t>26-Dec-2000</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
@@ -20656,7 +20666,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -20713,7 +20723,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -20765,37 +20775,37 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20MVA Power TR-1</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Powergear Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>05-Jul-1998</t>
+          <t>19-Feb-2019</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>300/1-1-1A</t>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P357" t="inlineStr">
@@ -20827,7 +20837,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -20847,7 +20857,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>300-150/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -20884,7 +20894,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -20904,7 +20914,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>300-150-75/1-1-1A</t>
+          <t>300-150/1-1-1A</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -20936,12 +20946,12 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20MVA Power TR-4</t>
+          <t>20MVA Power TR-1</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -20956,7 +20966,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>14-Sep-1998</t>
+          <t>05-Jul-1998</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -20998,7 +21008,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -21055,7 +21065,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -21107,37 +21117,37 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20MVAR Cap Bank-1</t>
+          <t>20MVA Power TR-4</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>NNP (No name plate)</t>
+          <t>Powergear Ltd</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>21-Jun-1984</t>
+          <t>14-Sep-1998</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>600-400-200-100/1-1-1A</t>
+          <t>300-150-75/1-1-1A</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>200/1-1-1A</t>
+          <t>300/1-1-1A</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
@@ -21169,7 +21179,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -21211,7 +21221,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -21221,32 +21231,37 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Main Bus</t>
+          <t>20MVAR Cap Bank-1</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Automatic Electric Ltd</t>
+          <t>NNP (No name plate)</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>01-Jun-1998</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V-110V</t>
+          <t>21-Jun-1984</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>600-400-200-100/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>200/1-1-1A</t>
         </is>
       </c>
       <c r="P365" t="inlineStr">
@@ -21278,7 +21293,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -21330,7 +21345,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -21377,27 +21392,27 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Main Bus</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Universal Magnoflux (UMF)</t>
+          <t>Automatic Electric Ltd</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>01-Jun-2004</t>
+          <t>01-Jun-1998</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -21434,7 +21449,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -21486,7 +21501,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -21523,52 +21538,42 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>100MVA</t>
+          <t>Bus-2/Transfer Bus</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Power TR-1 ABB</t>
+          <t>Universal Magnoflux (UMF)</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>18-Oct-2007</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>13044-005</t>
-        </is>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O371" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>01-Jun-2004</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -21600,22 +21605,22 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Power TR-2 NGEF</t>
+          <t>Power TR-1 ABB</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>05-Jun-1998</t>
+          <t>18-Oct-2007</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>6800000168</t>
+          <t>13044-005</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -21630,7 +21635,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -21652,42 +21657,47 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20MVA</t>
+          <t>100MVA</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Power TR-1 NGEF</t>
+          <t>Power TR-2 NGEF</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>05-Jul-1996</t>
+          <t>05-Jun-1998</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>2800055500</t>
+          <t>6800000168</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>12.1</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
@@ -21719,7 +21729,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Power TR-2 NGEF</t>
+          <t>Power TR-1 NGEF</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -21729,12 +21739,12 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>31-Oct-1995</t>
+          <t>05-Jul-1996</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>2800055501</t>
+          <t>2800055500</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -21776,22 +21786,22 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Power TR-3 NGEF</t>
+          <t>Power TR-2 NGEF</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>01-Mar-1998</t>
+          <t>31-Oct-1995</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>2800056329</t>
+          <t>2800055501</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -21833,22 +21843,22 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Power TR-4 NGEF</t>
+          <t>Power TR-3 NGEF</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>14-Sep-1998</t>
+          <t>01-Mar-1998</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>2800056681</t>
+          <t>2800056329</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -21885,42 +21895,37 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>31.5MVA</t>
+          <t>20MVA</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Power TR-5 ECE Industries Limited</t>
+          <t>Power TR-4 NGEF</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>29-Aug-2025</t>
+          <t>14-Sep-1998</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>S-87874</t>
+          <t>2800056681</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
           <t>Dyn11</t>
-        </is>
-      </c>
-      <c r="O377" t="inlineStr">
-        <is>
-          <t>12.5</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
@@ -21932,52 +21937,57 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>220kV Sarjapura</t>
+          <t>220kV NRS Rajajinagar</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Malur line-1 line</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>31.5MVA</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Power TR-5 ECE Industries Limited</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>31-Mar-2009</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>800-600-400-300/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>29-Aug-2025</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>S-87874</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>12.5</t>
         </is>
       </c>
       <c r="P378" t="inlineStr">
@@ -22009,7 +22019,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -22066,7 +22076,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -22118,12 +22128,12 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Malur line-2 line</t>
+          <t>Malur line-1 line</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -22180,7 +22190,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -22237,7 +22247,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -22289,12 +22299,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>Malur line-2 line</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -22309,7 +22319,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>11-May-2009</t>
+          <t>31-Mar-2009</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -22319,7 +22329,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>300/1-1-1-1-1A</t>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P384" t="inlineStr">
@@ -22351,7 +22361,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -22408,7 +22418,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -22460,12 +22470,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>100MVA Power TR-2</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -22480,7 +22490,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>19-Jul-2010</t>
+          <t>11-May-2009</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -22522,7 +22532,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -22579,7 +22589,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -22631,12 +22641,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>100MVA Power TR-2</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -22651,7 +22661,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>31-Mar-2009</t>
+          <t>19-Jul-2010</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -22661,7 +22671,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P390" t="inlineStr">
@@ -22693,7 +22703,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -22750,7 +22760,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -22792,7 +22802,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22802,17 +22812,17 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Mehru Electrical &amp; Mechanical Engg. Ltd</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -22825,9 +22835,14 @@
           <t>31-Mar-2009</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V-110V</t>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>800-600-400-300/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P393" t="inlineStr">
@@ -22859,7 +22874,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -22906,12 +22921,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -22948,27 +22963,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>66kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Chandapura line</t>
+          <t>Bus-2/Transfer Bus</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>Mehru Electrical &amp; Mechanical Engg. Ltd</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -22978,17 +22993,12 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>01-Oct-2016</t>
-        </is>
-      </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>800-600-400-200/1-1-1A</t>
-        </is>
-      </c>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>400/1-1-1A</t>
+          <t>31-Mar-2009</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -23020,7 +23030,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -23077,7 +23087,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -23129,12 +23139,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Dommasandra line</t>
+          <t>Chandapura line</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -23149,7 +23159,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>30-Sep-2016</t>
+          <t>01-Oct-2016</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -23191,7 +23201,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -23248,7 +23258,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -23300,12 +23310,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>100MVA Power TR-1</t>
+          <t>Dommasandra line</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -23320,17 +23330,17 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>11-May-2009</t>
+          <t>30-Sep-2016</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>1600-1000/1-1-1A</t>
+          <t>800-600-400-200/1-1-1A</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>1000/1-1-1A</t>
+          <t>400/1-1-1A</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
@@ -23362,7 +23372,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -23419,7 +23429,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -23471,12 +23481,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>100MVA Power TR-2</t>
+          <t>100MVA Power TR-1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -23491,7 +23501,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>19-Jul-2010</t>
+          <t>11-May-2009</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -23533,7 +23543,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -23590,7 +23600,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -23642,12 +23652,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>100MVA Power TR-2</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -23662,17 +23672,17 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>31-Mar-2009</t>
+          <t>19-Jul-2010</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>1600-1200/1-1-1A</t>
+          <t>1600-1000/1-1-1A</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>1600/1-1-1A</t>
+          <t>1000/1-1-1A</t>
         </is>
       </c>
       <c r="P408" t="inlineStr">
@@ -23704,7 +23714,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -23761,7 +23771,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -23803,7 +23813,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -23813,32 +23823,37 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Bus-1/Main Bus</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Vidyuth Controls Systems Pvt Ltd</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>22-Jan-2023</t>
-        </is>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>66kV/110V-110V-110V</t>
+          <t>31-Mar-2009</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>1600-1200/1-1-1A</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>1600/1-1-1A</t>
         </is>
       </c>
       <c r="P411" t="inlineStr">
@@ -23870,7 +23885,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -23885,7 +23900,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>22-Jan-2022</t>
+          <t>22-Jan-2023</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -23922,7 +23937,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -23969,27 +23984,27 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Bus-2/Transfer Bus</t>
+          <t>Bus-1/Main Bus</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>LAMCO</t>
+          <t>Vidyuth Controls Systems Pvt Ltd</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>19-Jul-2010</t>
+          <t>22-Jan-2022</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -24026,7 +24041,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -24078,7 +24093,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -24115,52 +24130,42 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>220/66/11kV</t>
+          <t>66kV</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>100MVA</t>
+          <t>Bus-2/Transfer Bus</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Power TR-1 AREVA</t>
+          <t>LAMCO</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>11-May-2009</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>B-30099</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="N417" t="inlineStr">
-        <is>
-          <t>YNyn0d11</t>
-        </is>
-      </c>
-      <c r="O417" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>19-Jul-2010</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>66kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P417" t="inlineStr">
@@ -24182,47 +24187,47 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>66/11kV</t>
+          <t>220/66/11kV</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>100MVA Power TR-2 EMCO 100.0 220/66/11kV YNyn0d11 10.1 2007 19-Jul-2010 In-service 1713/12775</t>
+          <t>100MVA</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>3 20MVA Power TR-1 Victory Electricals Ltd</t>
+          <t>Power TR-1 AREVA</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>17-May-2023</t>
+          <t>11-May-2009</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>4-0049/01</t>
+          <t>B-30099</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>Dyn11</t>
+          <t>YNyn0d11</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -24249,27 +24254,27 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20MVA</t>
+          <t>100MVA Power TR-2 EMCO 100.0 220/66/11kV YNyn0d11 10.1 2007 19-Jul-2010 In-service 1713/12775</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Power TR-2 IMP Powers Ltd</t>
+          <t>3 20MVA Power TR-1 Victory Electricals Ltd</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>04-Oct-2017</t>
+          <t>17-May-2023</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>PT-7769</t>
+          <t>4-0049/01</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -24284,7 +24289,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="P419" t="inlineStr">
@@ -24296,52 +24301,57 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>400kV DHP</t>
+          <t>220kV Sarjapura</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>66/11kV</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Power TR-3</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>20MVA</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Power TR-2 IMP Powers Ltd</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>24-Sep-2020</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>1600-800/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>1600/1-1-1-1-1A</t>
+          <t>04-Oct-2017</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>PT-7769</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Dyn11</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -24373,7 +24383,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -24430,7 +24440,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -24472,7 +24482,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -24482,12 +24492,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Main Bus-2</t>
+          <t>Power TR-3</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -24505,9 +24515,14 @@
           <t>24-Sep-2020</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V</t>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>1600-800/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>1600/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P423" t="inlineStr">
@@ -24539,7 +24554,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -24591,7 +24606,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -24628,27 +24643,27 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>400kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>B404-Nelamangala line</t>
+          <t>Main Bus-2</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Hyosung Corporation, Korea</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -24658,17 +24673,12 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>13-Nov-2020</t>
-        </is>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>3000-2000-1000/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>2000/1-1-1-1-1A</t>
+          <t>24-Sep-2020</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V</t>
         </is>
       </c>
       <c r="P426" t="inlineStr">
@@ -24700,7 +24710,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -24752,12 +24762,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>B407-PAVAGADA-1 line</t>
+          <t>B404-Nelamangala line</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -24772,7 +24782,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>17-Feb-2021</t>
+          <t>13-Nov-2020</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -24809,12 +24819,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>B412- SINGANAYAKANAHALLI line</t>
+          <t>B407-PAVAGADA-1 line</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -24829,7 +24839,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>17-Nov-2020</t>
+          <t>17-Feb-2021</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -24871,7 +24881,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -24923,12 +24933,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>B415-PAVAGADA-2 line</t>
+          <t>B412- SINGANAYAKANAHALLI line</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -24943,7 +24953,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>17-Feb-2021</t>
+          <t>17-Nov-2020</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -24980,12 +24990,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>B417-HOODY-2 line</t>
+          <t>B415-PAVAGADA-2 line</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -25000,7 +25010,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>23-Sep-2020</t>
+          <t>17-Feb-2021</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -25037,12 +25047,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>B418-HOODY-1 line</t>
+          <t>B417-HOODY-2 line</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -25094,12 +25104,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>B405- Tie-2 line</t>
+          <t>B418-HOODY-1 line</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -25114,7 +25124,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>13-Nov-2020</t>
+          <t>23-Sep-2020</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -25156,7 +25166,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -25176,7 +25186,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>2000-1000-500/1-1-1-1-1A</t>
+          <t>3000-2000-1000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -25213,7 +25223,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -25233,7 +25243,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>3000-2000-1000/1-1-1-1-1A</t>
+          <t>2000-1000-500/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -25265,12 +25275,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>B408- Tie-3 line</t>
+          <t>B405- Tie-2 line</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -25285,12 +25295,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>17-Mar-2021</t>
+          <t>13-Nov-2020</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>2000-1000-500/1-1-1-1-1A</t>
+          <t>3000-2000-1000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -25327,7 +25337,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -25384,7 +25394,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -25436,12 +25446,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>B413- Tie-4 line</t>
+          <t>B408- Tie-3 line</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -25456,7 +25466,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>17-Nov-2020</t>
+          <t>17-Mar-2021</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -25498,7 +25508,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -25518,7 +25528,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>3000-2000-1000/1-1-1-1-1A</t>
+          <t>2000-1000-500/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -25550,12 +25560,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>B416- Tie-5 line</t>
+          <t>B413- Tie-4 line</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -25570,7 +25580,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>17-Feb-2021</t>
+          <t>17-Nov-2020</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -25612,7 +25622,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -25669,7 +25679,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -25721,12 +25731,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>B419- Tie-6 line</t>
+          <t>B416- Tie-5 line</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -25741,12 +25751,12 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>13-Nov-2020</t>
+          <t>17-Feb-2021</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>2000-1000-500/1-1-1-1-1A</t>
+          <t>3000-2000-1000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25783,7 +25793,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -25803,7 +25813,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>3000-2000-1000/1-1-1-1-1A</t>
+          <t>2000-1000-500/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -25840,7 +25850,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -25860,7 +25870,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>2000-1000-500/1-1-1-1-1A</t>
+          <t>3000-2000-1000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25892,7 +25902,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Power TR-1</t>
+          <t>B419- Tie-6 line</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25912,7 +25922,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>24-Sep-2020</t>
+          <t>13-Nov-2020</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -25949,12 +25959,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Power TR-2</t>
+          <t>Power TR-1</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -25969,7 +25979,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>23-Sep-2020</t>
+          <t>24-Sep-2020</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -26006,12 +26016,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Power TR-3</t>
+          <t>Power TR-2</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -26026,7 +26036,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>24-Sep-2020</t>
+          <t>23-Sep-2020</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -26068,7 +26078,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -26120,12 +26130,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>B406-125MVAr Bus Reactor line</t>
+          <t>Power TR-3</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -26167,7 +26177,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -26177,32 +26187,37 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Main Bus-1</t>
+          <t>B406-125MVAr Bus Reactor line</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Nissin Electric Wuxi Co Ltd</t>
+          <t>Hyosung Corporation, Korea</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>23-Sep-2020</t>
-        </is>
-      </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t>400kV/110V-110V-110V</t>
+          <t>24-Sep-2020</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>2000-1000-500/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>2000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P453" t="inlineStr">
@@ -26234,7 +26249,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -26286,7 +26301,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -26333,12 +26348,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Main Bus-2</t>
+          <t>Main Bus-1</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -26390,7 +26405,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -26442,7 +26457,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -26479,37 +26494,42 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>400/220kV</t>
+          <t>400kV</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Power TR-1</t>
+          <t>Main Bus-2</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Nissin Electric Wuxi Co Ltd</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2020</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>24-Sep-2020</t>
-        </is>
-      </c>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>14081-01</t>
-        </is>
-      </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>500.0</t>
+          <t>23-Sep-2020</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>400kV/110V-110V-110V</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -26531,12 +26551,12 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>400/220/33kV</t>
+          <t>400/220kV</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Power TR-3</t>
+          <t>Power TR-1</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -26544,34 +26564,19 @@
           <t>ABB</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>31-Mar-2023</t>
+          <t>24-Sep-2020</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>14104-01</t>
+          <t>14081-01</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>500.0</t>
-        </is>
-      </c>
-      <c r="N460" t="inlineStr">
-        <is>
-          <t>YNa0d11</t>
-        </is>
-      </c>
-      <c r="O460" t="inlineStr">
-        <is>
-          <t>15.4</t>
         </is>
       </c>
       <c r="P460" t="inlineStr">
@@ -26583,52 +26588,57 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>400kV Hoody</t>
+          <t>400kV DHP</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>220kV</t>
+          <t>400/220/33kV</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Hoody-HAL line-1 line</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>Power TR-3</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>13-Jul-1995</t>
-        </is>
-      </c>
-      <c r="J461" t="inlineStr">
-        <is>
-          <t>1600-800/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>800/1-1-1-1-1A</t>
+          <t>31-Mar-2023</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>14104-01</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>YNa0d11</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>15.4</t>
         </is>
       </c>
       <c r="P461" t="inlineStr">
@@ -26660,7 +26670,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -26717,7 +26727,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -26769,12 +26779,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Hoody-HAL line-2 line</t>
+          <t>Hoody-HAL line-1 line</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -26789,7 +26799,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>25-Jul-1995</t>
+          <t>13-Jul-1995</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -26831,7 +26841,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -26888,7 +26898,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -26940,27 +26950,27 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Hoody-Shobha Dreams line</t>
+          <t>Hoody-HAL line-2 line</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Electricals Kerala Ltd</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>31-Aug-2008</t>
+          <t>25-Jul-1995</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -27002,7 +27012,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -27059,7 +27069,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -27111,12 +27121,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Hoody-EPIP line</t>
+          <t>Hoody-Shobha Dreams line</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -27131,7 +27141,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>14-Dec-2008</t>
+          <t>31-Aug-2008</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -27173,7 +27183,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -27230,7 +27240,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -27282,32 +27292,32 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>ITPL UG Cable line</t>
+          <t>Hoody-EPIP line</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Mechanical Engg.</t>
+          <t>Electricals Kerala Ltd</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>30-Oct-2017</t>
+          <t>14-Dec-2008</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>800-600-400-300/1-1-1-1-1A</t>
+          <t>1600-800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -27344,7 +27354,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -27396,37 +27406,37 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Power TR-1</t>
+          <t>ITPL UG Cable line</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>Mechanical Engg.</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>31-Mar-1995</t>
+          <t>30-Oct-2017</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>1600-1400/1-1-1-1-1A</t>
+          <t>800-600-400-300/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>1400/1-1-1-1-1A</t>
+          <t>800/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P475" t="inlineStr">
@@ -27458,7 +27468,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -27515,7 +27525,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -27557,7 +27567,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Potential Transformer (PT)</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -27567,32 +27577,37 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Main Bus-1</t>
+          <t>Power TR-1</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>25-Mar-2017</t>
-        </is>
-      </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>220kV/110V-110V</t>
+          <t>31-Mar-1995</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>1600-1400/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>1400/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P478" t="inlineStr">
@@ -27624,7 +27639,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -27676,7 +27691,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -27723,12 +27738,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Bus Coupler</t>
+          <t>Main Bus-1</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -27780,7 +27795,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -27832,7 +27847,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -27869,47 +27884,42 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Current Transformer (CT)</t>
+          <t>Potential Transformer (PT)</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>400kV</t>
+          <t>220kV</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Hoody-Kolar-1 line</t>
+          <t>Bus Coupler</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>CGL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>16-Oct-2002</t>
-        </is>
-      </c>
-      <c r="J484" t="inlineStr">
-        <is>
-          <t>3000-2000-1000/1-1-1-1-1A</t>
-        </is>
-      </c>
-      <c r="K484" t="inlineStr">
-        <is>
-          <t>1000/1-1-1-1-1A</t>
+          <t>25-Mar-2017</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>220kV/110V-110V</t>
         </is>
       </c>
       <c r="P484" t="inlineStr">
@@ -27941,7 +27951,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -27998,7 +28008,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -28050,12 +28060,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Hoody-Kolar-2 line</t>
+          <t>Hoody-Kolar-1 line</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -28112,7 +28122,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -28169,7 +28179,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -28211,17 +28221,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Current Transformer (CT)</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>400/220/33kV</t>
+          <t>400kV</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Power TR-1 ( R-Phase )</t>
+          <t>Hoody-Kolar-2 line</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -28231,32 +28246,22 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>31-Mar-1995</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr">
-        <is>
-          <t>T8386/4</t>
-        </is>
-      </c>
-      <c r="M490" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
-      </c>
-      <c r="N490" t="inlineStr">
-        <is>
-          <t>YNa0d11</t>
-        </is>
-      </c>
-      <c r="O490" t="inlineStr">
-        <is>
-          <t>13.7</t>
+          <t>16-Oct-2002</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>3000-2000-1000/1-1-1-1-1A</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>1000/1-1-1-1-1A</t>
         </is>
       </c>
       <c r="P490" t="inlineStr">
@@ -28283,7 +28288,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Power TR-1 ( B-Phase )</t>
+          <t>Power TR-1 ( R-Phase )</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -28293,17 +28298,17 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>15-May-2006</t>
+          <t>31-Mar-1995</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>T9149/1</t>
+          <t>T8386/4</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -28345,27 +28350,27 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Power TR-2 ( R-Phase )</t>
+          <t>Power TR-1 ( B-Phase )</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Alstom</t>
+          <t>CGL</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>14-Apr-2018</t>
+          <t>15-May-2006</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>B-31107</t>
+          <t>T9149/1</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -28407,7 +28412,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Power TR-2 ( B-Phase )</t>
+          <t>Power TR-2 ( R-Phase )</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -28417,17 +28422,17 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>08-Oct-2016</t>
+          <t>14-Apr-2018</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>B-31038</t>
+          <t>B-31107</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
@@ -28442,7 +28447,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="P493" t="inlineStr">
@@ -28469,7 +28474,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Power TR-3 ( Y-Phase )</t>
+          <t>Power TR-2 ( B-Phase )</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -28479,17 +28484,17 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>24-Jan-2015</t>
+          <t>08-Oct-2016</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>B-30635</t>
+          <t>B-31038</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -28504,7 +28509,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="P494" t="inlineStr">
@@ -28531,45 +28536,107 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
+          <t>Power TR-3 ( Y-Phase )</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Alstom</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>24-Jan-2015</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>B-30635</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>YNa0d11</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>In-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>400kV Hoody</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>400/220/33kV</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
           <t>Power TR-3 ( Spare )</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr">
+      <c r="F496" t="inlineStr">
         <is>
           <t>Alstom</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr">
+      <c r="G496" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr">
+      <c r="H496" t="inlineStr">
         <is>
           <t>27-Jan-2015</t>
         </is>
       </c>
-      <c r="I495" t="inlineStr">
+      <c r="I496" t="inlineStr">
         <is>
           <t>B-30637</t>
         </is>
       </c>
-      <c r="M495" t="inlineStr">
+      <c r="M496" t="inlineStr">
         <is>
           <t>167.0</t>
         </is>
       </c>
-      <c r="N495" t="inlineStr">
+      <c r="N496" t="inlineStr">
         <is>
           <t>YNa0d11</t>
         </is>
       </c>
-      <c r="O495" t="inlineStr">
+      <c r="O496" t="inlineStr">
         <is>
           <t>13.6</t>
         </is>
       </c>
-      <c r="P495" t="inlineStr">
+      <c r="P496" t="inlineStr">
         <is>
           <t>In-service</t>
         </is>

--- a/equipment_seed.xlsx
+++ b/equipment_seed.xlsx
@@ -447,17 +447,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BRAZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RT North Division</t>
+          <t>Begur</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -469,39 +469,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BMAZ South</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RT East Division</t>
+          <t>Hoody</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>Ramanagara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RT East Division</t>
+          <t>Yerandanahally</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -513,39 +513,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>Ramanagara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RT South Division</t>
+          <t>Kanakapura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kolar Transmission Circle</t>
+          <t>BRAZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kolar Division</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -557,17 +557,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kolar Transmission Circle</t>
+          <t>BRAZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kolar Division</t>
+          <t>Malur</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -579,39 +579,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BMAZ North</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RT North Division</t>
+          <t>Hebbal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BMAZ North</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RT South Division</t>
+          <t>NRS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -623,17 +623,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>Ramanagara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RT East Division</t>
+          <t>Yerandanahally</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -645,17 +645,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BMAZ South</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RT East Division</t>
+          <t>Hoody</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,17 +667,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bengaluru Zone</t>
+          <t>Bangalore Zone</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bengaluru Transmission Circle</t>
+          <t>BMAZ South</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RT East Division</t>
+          <t>Hoody</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3788,7 +3788,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3845,7 +3845,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3959,7 +3959,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4073,7 +4073,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4130,7 +4130,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4244,7 +4244,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4358,7 +4358,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4472,7 +4472,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4529,7 +4529,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4643,7 +4643,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4804,7 +4804,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4960,7 +4960,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5012,7 +5012,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5069,7 +5069,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5183,7 +5183,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5297,7 +5297,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5354,7 +5354,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5582,7 +5582,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5696,7 +5696,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5810,7 +5810,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5867,7 +5867,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6090,7 +6090,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6474,7 +6474,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>220kV EDC</t>
+          <t>220kV Sir M V EDC GIS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8853,7 +8853,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8910,7 +8910,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8967,7 +8967,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9024,7 +9024,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9081,7 +9081,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9138,7 +9138,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9195,7 +9195,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9252,7 +9252,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9309,7 +9309,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9418,7 +9418,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9470,7 +9470,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9522,7 +9522,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9574,7 +9574,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9626,7 +9626,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9678,7 +9678,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9735,7 +9735,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9792,7 +9792,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9849,7 +9849,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9963,7 +9963,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10077,7 +10077,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10134,7 +10134,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10248,7 +10248,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10362,7 +10362,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10414,7 +10414,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10466,7 +10466,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10570,7 +10570,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10622,7 +10622,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10674,7 +10674,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10731,7 +10731,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>220kV Kanakapura</t>
+          <t>66kV Kanakapura</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,7 +15107,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -15164,7 +15164,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -15221,7 +15221,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -15335,7 +15335,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -15392,7 +15392,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -15449,7 +15449,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -15506,7 +15506,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -15563,7 +15563,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15620,7 +15620,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -15677,7 +15677,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -15791,7 +15791,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -15848,7 +15848,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -15905,7 +15905,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -15962,7 +15962,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -16133,7 +16133,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -16190,7 +16190,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -16247,7 +16247,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -16304,7 +16304,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -16361,7 +16361,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -16418,7 +16418,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -16475,7 +16475,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -16532,7 +16532,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -16589,7 +16589,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -16703,7 +16703,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -16760,7 +16760,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -16817,7 +16817,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -16931,7 +16931,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -16988,7 +16988,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -17045,7 +17045,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -17102,7 +17102,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -17159,7 +17159,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -17216,7 +17216,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -17273,7 +17273,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -17330,7 +17330,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -17387,7 +17387,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -17444,7 +17444,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -17501,7 +17501,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -17563,7 +17563,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -17625,7 +17625,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -17687,7 +17687,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>220kV Manyatha Tech Park</t>
+          <t>220kV Manyatha Tech Park GIS Station</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
